--- a/artfynd/A 71570-2021 artfynd.xlsx
+++ b/artfynd/A 71570-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 71570-2021 artfynd.xlsx
+++ b/artfynd/A 71570-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110551114</v>
+        <v>110551111</v>
       </c>
       <c r="B2" t="n">
-        <v>103273</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446520.0667026629</v>
+        <v>446565</v>
       </c>
       <c r="R2" t="n">
-        <v>7032685.200475898</v>
+        <v>7032744</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2023-06-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-06-27</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112105682</v>
+        <v>112105381</v>
       </c>
       <c r="B3" t="n">
-        <v>89143</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5747</v>
+        <v>3286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,14 +806,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svensbergsbäcken (Svensbergsbäcken), Jmt</t>
+          <t>Landverktjärnen, Landverktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446627</v>
+        <v>446564</v>
       </c>
       <c r="R3" t="n">
-        <v>7032919</v>
+        <v>7032716</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,37 +873,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112105366</v>
+        <v>112105682</v>
       </c>
       <c r="B4" t="n">
-        <v>85633</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>236435</v>
+        <v>5747</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Droppklibbskivling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Limacella guttata</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers. : Fr.) Konrad &amp; Maubl.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,14 +907,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Landverktjärnen (Landverktjärnen), Jmt</t>
+          <t>Svensbergsbäcken, Svensbergsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446547</v>
+        <v>446627</v>
       </c>
       <c r="R4" t="n">
-        <v>7032732</v>
+        <v>7032920</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,12 +977,7 @@
         <v>112105307</v>
       </c>
       <c r="B5" t="n">
-        <v>89153</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,11 +1008,11 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Landverktjärnen (Landverktjärnen), Jmt</t>
+          <t>Landverktjärnen, Landverktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446544</v>
+        <v>446545</v>
       </c>
       <c r="R5" t="n">
         <v>7032738</v>
@@ -1113,16 +1078,11 @@
         <v>112213267</v>
       </c>
       <c r="B6" t="n">
-        <v>90874</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1135,12 +1095,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,7 +1113,7 @@
         <v>446536</v>
       </c>
       <c r="R6" t="n">
-        <v>7032714</v>
+        <v>7032713</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,6 +1169,306 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110551101</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ol-Olsvarttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>446553</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7032732</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>110551114</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ol-Olsvarttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>446520</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7032685</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112105366</v>
+      </c>
+      <c r="B9" t="n">
+        <v>89871</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>236435</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Droppklibbskivling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Limacella guttata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pers. : Fr.) Konrad &amp; Maubl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Landverktjärnen, Landverktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>446547</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7032732</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 71570-2021 artfynd.xlsx
+++ b/artfynd/A 71570-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110551111</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112105381</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112105682</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112105307</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213267</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110551101</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1368,6 +1403,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110551114</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1469,8 +1509,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112105366</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>